--- a/excel/1000(n)/AVG_Random_Dataset.xlsx
+++ b/excel/1000(n)/AVG_Random_Dataset.xlsx
@@ -102,19 +102,19 @@
         <v>1000.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>1032990.0</v>
+        <v>868335.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>219230.0</v>
+        <v>56260.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>347055.0</v>
+        <v>246965.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>114880.0</v>
+        <v>94330.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>146565.0</v>
+        <v>125125.0</v>
       </c>
     </row>
   </sheetData>

--- a/excel/1000(n)/AVG_Random_Dataset.xlsx
+++ b/excel/1000(n)/AVG_Random_Dataset.xlsx
@@ -102,19 +102,19 @@
         <v>1000.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>868335.0</v>
+        <v>946010.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>56260.0</v>
+        <v>68490.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>246965.0</v>
+        <v>304355.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>94330.0</v>
+        <v>107740.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>125125.0</v>
+        <v>131210.0</v>
       </c>
     </row>
   </sheetData>
